--- a/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DITMG</t>
+          <t>TATPG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`System- och verksamhetsutveckling` → `GIK2JW` (nedlagd 2025-12-08) — plain-text-referens; rad: - System- och verksamhetsutveckling, 7,5hp</t>
+          <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens; rad: - Produktutveckling, 7,5 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DSVPG</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`System- och verksamhetsutveckling` → `GIK2JW` (nedlagd 2025-12-08) — plain-text-referens; rad: - System- och verksamhetsutveckling, 7,5 hp</t>
+          <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens; rad: - Industriell Ekonomi med kalkylering, 7,5hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KGDWG</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`System- och verksamhetsutveckling` → `GIK2JW` (nedlagd 2025-12-08) — plain-text-referens; rad: - System- och verksamhetsutveckling, 7,5 hp</t>
+          <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens; rad: - Introduktion till mekanik och hållfasthetslära, 7,5hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KGDWG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TATPG</t>
+          <t>TPOKG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens; rad: - Produktutveckling, 7,5 hp</t>
+          <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens; rad: - 3D CAD Grundläggande, 7,5hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens; rad: - Industriell Ekonomi med kalkylering, 7,5hp</t>
+          <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens; rad: - Statistik för ingenjörer, 7,5hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens; rad: - Introduktion till mekanik och hållfasthetslära, 7,5hp</t>
+          <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens; rad: - Tillverkningsteknik, 7,5hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens; rad: - 3D CAD Grundläggande, 7,5hp</t>
+          <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens; rad: - Grundläggande materiallära, 7,5hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens; rad: - Statistik för ingenjörer, 7,5hp</t>
+          <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens; rad: - CAD/CAM, 7,5hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens; rad: - Tillverkningsteknik, 7,5hp</t>
+          <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens; rad: - Hydraulik och Pneumatik, 7,5hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens; rad: - Grundläggande materiallära, 7,5hp</t>
+          <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens; rad: - Grundläggande ellära för maskinteknik, 3,5hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens; rad: - CAD/CAM, 7,5hp</t>
+          <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens; rad: - Materialval, 4hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens; rad: - Hydraulik och Pneumatik, 7,5hp</t>
+          <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens; rad: - Introduktion till hållbar utveckling inom maskinteknik, 7,5hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens; rad: - Grundläggande ellära för maskinteknik, 3,5hp</t>
+          <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens; rad: - Konstruktionsprojekt, 7,5hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens; rad: - Materialval, 4hp</t>
+          <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens; rad: - Kvalitetsteknik, 7,5hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens; rad: - Introduktion till hållbar utveckling inom maskinteknik, 7,5hp</t>
+          <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens; rad: - Industriell produktion, 7,5hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -874,89 +874,8 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TPOKG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens; rad: - Konstruktionsprojekt, 7,5hp</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TPOKG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens; rad: - Kvalitetsteknik, 7,5hp</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TPOKG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens; rad: - Industriell produktion, 7,5hp</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -988,12 +907,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens; rad: - Produktutveckling, 7,5 hp</t>
+          <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens; rad: - Industriell Ekonomi med kalkylering, 7,5hp</t>
+          <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens; rad: - Introduktion till mekanik och hållfasthetslära, 7,5hp</t>
+          <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens; rad: - 3D CAD Grundläggande, 7,5hp</t>
+          <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens; rad: - Statistik för ingenjörer, 7,5hp</t>
+          <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens; rad: - Tillverkningsteknik, 7,5hp</t>
+          <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens; rad: - Grundläggande materiallära, 7,5hp</t>
+          <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens; rad: - CAD/CAM, 7,5hp</t>
+          <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens; rad: - Hydraulik och Pneumatik, 7,5hp</t>
+          <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens; rad: - Grundläggande ellära för maskinteknik, 3,5hp</t>
+          <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens; rad: - Materialval, 4hp</t>
+          <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens; rad: - Introduktion till hållbar utveckling inom maskinteknik, 7,5hp</t>
+          <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens; rad: - Konstruktionsprojekt, 7,5hp</t>
+          <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens; rad: - Kvalitetsteknik, 7,5hp</t>
+          <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens; rad: - Industriell produktion, 7,5hp</t>
+          <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
@@ -509,15 +527,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -536,15 +564,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -563,15 +601,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -590,15 +638,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -617,15 +675,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -644,15 +712,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -671,15 +749,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -698,15 +786,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -725,15 +823,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -752,15 +860,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -779,15 +897,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -806,15 +934,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -833,15 +971,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -860,53 +1008,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Programmet listar nedlagd kurs</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -508,7 +514,12 @@
           <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`MT2016` (nedlagd 2021-11-30) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TATPG</t>
         </is>
@@ -545,7 +556,12 @@
           <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`IE1062` (nedlagd 2024-11-06) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -582,7 +598,12 @@
           <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`MT1067` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -619,7 +640,12 @@
           <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`MT1051` (nedlagd 2025-08-21) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -656,7 +682,12 @@
           <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`ST1028` (nedlagd 2024-11-06) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -693,7 +724,12 @@
           <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`MT1070` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -730,7 +766,12 @@
           <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`GMP2LL` (nedlagd 2025-09-30) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -767,7 +808,12 @@
           <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`MT1072` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -804,7 +850,12 @@
           <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`MT1073` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -841,7 +892,12 @@
           <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`ET1022` (nedlagd 2024-11-06) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -878,7 +934,12 @@
           <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`MP2039` (nedlagd 2025-09-30) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -915,7 +976,12 @@
           <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`GMT2CU` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -952,7 +1018,12 @@
           <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`GMT224` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -989,7 +1060,12 @@
           <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`GMT2CV` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
@@ -1026,45 +1102,50 @@
           <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`GMT259` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TPOKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:H16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Nedlagda kursreferenser.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Produktutveckling` → `MT2016` (nedlagd 2021-11-30) — plain-text-referens</t>
+          <t>`Produktutveckling`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Industriell Ekonomi med kalkylering` → `IE1062` (nedlagd 2024-11-06) — plain-text-referens</t>
+          <t>`Industriell Ekonomi med kalkylering`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Introduktion till mekanik och hållfasthetslära` → `MT1067` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Introduktion till mekanik och hållfasthetslära`</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`3D CAD Grundläggande` → `MT1051` (nedlagd 2025-08-21) — plain-text-referens</t>
+          <t>`3D CAD Grundläggande`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Statistik för ingenjörer` → `ST1028` (nedlagd 2024-11-06) — plain-text-referens</t>
+          <t>`Statistik för ingenjörer`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Tillverkningsteknik` → `MT1070` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Tillverkningsteknik`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Grundläggande materiallära` → `GMP2LL` (nedlagd 2025-09-30) — plain-text-referens</t>
+          <t>`Grundläggande materiallära`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`CAD/CAM` → `MT1072` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`CAD/CAM`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Hydraulik och Pneumatik` → `MT1073` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Hydraulik och Pneumatik`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Grundläggande ellära för maskinteknik` → `ET1022` (nedlagd 2024-11-06) — plain-text-referens</t>
+          <t>`Grundläggande ellära för maskinteknik`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Materialval` → `MP2039` (nedlagd 2025-09-30) — plain-text-referens</t>
+          <t>`Materialval`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Introduktion till hållbar utveckling inom maskinteknik` → `GMT2CU` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Introduktion till hållbar utveckling inom maskinteknik`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Konstruktionsprojekt` → `GMT224` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Konstruktionsprojekt`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Kvalitetsteknik` → `GMT2CV` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Kvalitetsteknik`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Industriell produktion` → `GMT259` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Industriell produktion`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
